--- a/Analise de preços site/Ordenação de Produtos/ORDENAÇÃO DE PRODUTOS.xlsx
+++ b/Analise de preços site/Ordenação de Produtos/ORDENAÇÃO DE PRODUTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Protork\Desktop\Analise de preços site\Ordenação de Produtos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1548C54A-55F3-46BD-93F8-B3EAB94EE018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB39563-7404-4694-82F3-79112993FDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
   <si>
     <t>SKU do Pai</t>
   </si>
@@ -41,65 +41,68 @@
     <t>Coleção</t>
   </si>
   <si>
-    <t>125622</t>
-  </si>
-  <si>
-    <t>119610A</t>
-  </si>
-  <si>
-    <t>124885</t>
-  </si>
-  <si>
-    <t>127063</t>
-  </si>
-  <si>
-    <t>121016</t>
-  </si>
-  <si>
-    <t>119822</t>
-  </si>
-  <si>
-    <t>126178</t>
+    <t>Ordenação</t>
+  </si>
+  <si>
+    <t>212A</t>
+  </si>
+  <si>
+    <t>126794</t>
+  </si>
+  <si>
+    <t>4902A</t>
+  </si>
+  <si>
+    <t>126957</t>
+  </si>
+  <si>
+    <t>126759</t>
+  </si>
+  <si>
+    <t>126182</t>
+  </si>
+  <si>
+    <t>2218</t>
+  </si>
+  <si>
+    <t>126769</t>
+  </si>
+  <si>
+    <t>115695A</t>
+  </si>
+  <si>
+    <t>126926</t>
+  </si>
+  <si>
+    <t>5323</t>
+  </si>
+  <si>
+    <t>126935</t>
+  </si>
+  <si>
+    <t>126771</t>
+  </si>
+  <si>
+    <t>126934</t>
   </si>
   <si>
     <t>119603A</t>
   </si>
   <si>
-    <t>5501A</t>
-  </si>
-  <si>
-    <t>110002</t>
-  </si>
-  <si>
-    <t>119943</t>
-  </si>
-  <si>
-    <t>116746A</t>
-  </si>
-  <si>
-    <t>317</t>
-  </si>
-  <si>
-    <t>127051</t>
-  </si>
-  <si>
-    <t>117524A</t>
-  </si>
-  <si>
-    <t>Oferta do Dia</t>
-  </si>
-  <si>
-    <t>Ordenação</t>
-  </si>
-  <si>
-    <t>4902A</t>
+    <t>119668A</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>Feito para Campeões</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,16 +110,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00FF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -124,13 +140,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -139,6 +176,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF00FF00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -435,199 +477,210 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B17" s="2">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="2">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1">
-        <v>12</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1">
-        <v>8</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1">
-        <v>13</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>17</v>
+      <c r="C18" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
